--- a/Блокноты/Банеры/2026/27.03.26/Ключи Блокноты .xlsx
+++ b/Блокноты/Банеры/2026/27.03.26/Ключи Блокноты .xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="9120"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>324 NtrAntaly324.PQTC.27.03.26 Анталья</t>
   </si>
@@ -39,6 +39,96 @@
   </si>
   <si>
     <t>326 NtrAntaly326.PQTC.27.03.26 Анталья</t>
+  </si>
+  <si>
+    <t>327 NtrAntaly327.PQTC.27.03.26 Анталья</t>
+  </si>
+  <si>
+    <t>328 NtrAntaly328.PQTC.27.03.26 Анталья горы</t>
+  </si>
+  <si>
+    <t>Анталья,  Antalya, Анталия, Турция, Turkiye, достопремечательности, красивый вид, пейзаж, город, горы</t>
+  </si>
+  <si>
+    <t>329 NtrAntaly329.PQTC.27.03.26 Анталья канатная дорога</t>
+  </si>
+  <si>
+    <t>330 NtrAntaly330.PQTC.27.03.26 Анталья канатная дорога</t>
+  </si>
+  <si>
+    <t>331 NtrAntaly331.PQTC.27.03.26 Анталья амфитеатр Сиде</t>
+  </si>
+  <si>
+    <t>Анталья,  Antalya, Анталия, Турция, Turkiye, достопремечательности, красивый вид, пейзаж, город, порт, побережье, берег, бухта, средиземное море, море, скалы, горы, пляж, амфитеатр, Амфитиатр Сиде, древний город, античный город, архитектура, античная архитектура</t>
+  </si>
+  <si>
+    <t>332 NtrAntaly332.PQTC.27.03.26 Анталья Аспендос</t>
+  </si>
+  <si>
+    <t>Анталья,  Antalya, Анталия, Турция, Turkiye, достопремечательности, красивый вид, пейзаж, город,  руины, развалины, Аспендос, aspendos antik kenti, древний город, античный город, архитектура, античная архитектура</t>
+  </si>
+  <si>
+    <t>333 NtrAntaly333.PQTC.27.03.26 Анталья Дом-музей Ататюрка</t>
+  </si>
+  <si>
+    <t>Анталья,  Antalya, Анталия, Турция, Turkiye, достопремечательности, Дом-музей Ататюрка, дом-музей, дом, музей, etnografya muzesi, ethnographic museum, odunpazari evleri</t>
+  </si>
+  <si>
+    <t>334 NtrAntaly334.PQTC.27.03.26 Анталья Археологический музей</t>
+  </si>
+  <si>
+    <t>Анталья,  Antalya, Анталия, Турция, Turkiye, достопремечательности, археологический музей, музей, аргеология, древности, античный музей</t>
+  </si>
+  <si>
+    <t>335 NtrDontSt335.PQTC.27.03.26 Dont_Starve_Уилсон</t>
+  </si>
+  <si>
+    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game, Уилсон,  Wilson, ДСТ</t>
+  </si>
+  <si>
+    <t>336 NtrDontSt336.PQTC.27.03.26 Dont_Starve_Венди</t>
+  </si>
+  <si>
+    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game, Венди, Wendy, ДСТ</t>
+  </si>
+  <si>
+    <t>337 NtrDontSt337.PQTC.27.03.26 Dont_Starve_Венди_2</t>
+  </si>
+  <si>
+    <t>338 NtrDontSt338.PQTC.27.03.26 Dont_Starve_ Уиллоу</t>
+  </si>
+  <si>
+    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game,  Уиллоу, Willow, ДСТ</t>
+  </si>
+  <si>
+    <t>339 NtrDontSt339.PQTC.27.03.26 Dont_Starve_ Уиллоу_2</t>
+  </si>
+  <si>
+    <t>340 NtrDontSt340.PQTC.27.03.26 Dont_Starve_ Уиллоу_3</t>
+  </si>
+  <si>
+    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game,  Уиллоу, Willow, Уилсон, Wilson, ДСТ</t>
+  </si>
+  <si>
+    <t>341 NtrDontSt341.PQTC.27.03.26 Dont_Starve_Вуди</t>
+  </si>
+  <si>
+    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game, Вуди, Woodie, ДТС</t>
+  </si>
+  <si>
+    <t>342 NtrDontSt342.PQTC.27.03.26 Dont_Starve_Персонажи</t>
+  </si>
+  <si>
+    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game, персонажи don`t starve,ДТС</t>
+  </si>
+  <si>
+    <t>343 NtrDontSt343.PQTC.27.03.26 Dont_Starve_Персонажи_2</t>
+  </si>
+  <si>
+    <t>344 NtrDontSt344.PQTC.27.03.26 Dont_Starve_Циклоп-олень</t>
+  </si>
+  <si>
+    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game, Циклоп-олень, Deerclops,ДТС</t>
   </si>
 </sst>
 </file>
@@ -51,7 +141,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,7 +164,7 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
@@ -85,6 +175,11 @@
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -565,137 +660,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -712,7 +807,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -730,13 +830,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1043,236 +1143,308 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="5"/>
-      <c r="B4" s="4"/>
+      <c r="A4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4"/>
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4"/>
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="5"/>
-      <c r="B7" s="4"/>
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
+      <c r="A9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="3"/>
-      <c r="B10" s="4"/>
+      <c r="A10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="7"/>
-      <c r="B11" s="4"/>
+      <c r="A11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="8"/>
-      <c r="B12" s="4"/>
+      <c r="A12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
+      <c r="A13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
+      <c r="A14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
+      <c r="A15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10"/>
+      <c r="A16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10"/>
+      <c r="A17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10"/>
+      <c r="A18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="9"/>
-      <c r="B19" s="10"/>
+      <c r="A19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="9"/>
-      <c r="B20" s="10"/>
+      <c r="A20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="9"/>
-      <c r="B21" s="10"/>
+      <c r="A21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="9"/>
-      <c r="B22" s="10"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="11"/>
-      <c r="B23" s="10"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="11"/>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="13"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="14"/>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="11"/>
-      <c r="B25" s="13"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="14"/>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="3"/>
-      <c r="B36" s="14"/>
+      <c r="B36" s="15"/>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="3"/>
-      <c r="B37" s="15"/>
+      <c r="B37" s="16"/>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="3"/>
-      <c r="B38" s="15"/>
+      <c r="B38" s="16"/>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="16"/>
-      <c r="B39" s="17"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="18"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="16"/>
-      <c r="B40" s="17"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="18"/>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="16"/>
-      <c r="B41" s="17"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="18"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="16"/>
-      <c r="B42" s="17"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="18"/>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="16"/>
-      <c r="B43" s="17"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="18"/>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="16"/>
-      <c r="B44" s="17"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="18"/>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="17"/>
-      <c r="B45" s="18"/>
+      <c r="A45" s="18"/>
+      <c r="B45" s="19"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="16"/>
-      <c r="B46" s="18"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="19"/>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="16"/>
-      <c r="B47" s="18"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="19"/>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="16"/>
-      <c r="B48" s="18"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="19"/>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="17"/>
-      <c r="B49" s="18"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="19"/>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="16"/>
-      <c r="B50" s="18"/>
+      <c r="A50" s="17"/>
+      <c r="B50" s="19"/>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="5"/>
-      <c r="B51" s="13"/>
+      <c r="B51" s="14"/>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="3"/>
-      <c r="B52" s="13"/>
+      <c r="B52" s="14"/>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="3"/>
-      <c r="B53" s="13"/>
+      <c r="B53" s="14"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="3"/>
-      <c r="B54" s="13"/>
+      <c r="B54" s="14"/>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="3"/>
-      <c r="B55" s="13"/>
+      <c r="B55" s="14"/>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="3"/>
-      <c r="B56" s="13"/>
+      <c r="B56" s="14"/>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="3"/>
-      <c r="B57" s="13"/>
+      <c r="B57" s="14"/>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="3"/>
-      <c r="B58" s="13"/>
+      <c r="B58" s="14"/>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="17"/>
-      <c r="B59" s="18"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="19"/>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="16"/>
-      <c r="B60" s="18"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="19"/>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="16"/>
-      <c r="B61" s="18"/>
+      <c r="A61" s="17"/>
+      <c r="B61" s="19"/>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="16"/>
-      <c r="B62" s="13"/>
+      <c r="A62" s="17"/>
+      <c r="B62" s="14"/>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="16"/>
-      <c r="B63" s="13"/>
+      <c r="A63" s="17"/>
+      <c r="B63" s="14"/>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="16"/>
-      <c r="B64" s="13"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="14"/>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="16"/>
-      <c r="B65" s="13"/>
+      <c r="A65" s="17"/>
+      <c r="B65" s="14"/>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="19"/>
-      <c r="B66" s="10"/>
+      <c r="A66" s="20"/>
+      <c r="B66" s="11"/>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="19"/>
-      <c r="B67" s="10"/>
+      <c r="A67" s="20"/>
+      <c r="B67" s="11"/>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="19"/>
-      <c r="B68" s="10"/>
+      <c r="A68" s="20"/>
+      <c r="B68" s="11"/>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="19"/>
-      <c r="B69" s="10"/>
+      <c r="A69" s="20"/>
+      <c r="B69" s="11"/>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="19"/>
-      <c r="B70" s="10"/>
+      <c r="A70" s="20"/>
+      <c r="B70" s="11"/>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="19"/>
-      <c r="B71" s="10"/>
+      <c r="A71" s="20"/>
+      <c r="B71" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
